--- a/APPdata_WIDMA_Jaipur/Thresholds_WIDMA.xlsx
+++ b/APPdata_WIDMA_Jaipur/Thresholds_WIDMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPdata_WIDMA_Jaipur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wipro365-my.sharepoint.com/personal/ma80050179_wipro_com/Documents/Documents/GitHub/WIDMA_JPR/APPdata_WIDMA_Jaipur/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19070AD-0AC9-4F2E-B9AF-B1F956F8843B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{E19070AD-0AC9-4F2E-B9AF-B1F956F8843B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F029D7C-8FD8-48E1-BC15-EE3CEE724EA9}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3768" windowWidth="17280" windowHeight="9912" xr2:uid="{0C922889-AB5D-40DE-930E-B68A6D2B34E6}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="9912" xr2:uid="{0C922889-AB5D-40DE-930E-B68A6D2B34E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="33">
   <si>
     <t>Asset name</t>
   </si>
@@ -92,12 +92,6 @@
     <t>Spindle Bed Ball Nut.</t>
   </si>
   <si>
-    <t>Burnish 'Coolant Motor</t>
-  </si>
-  <si>
-    <t>Burnish Hydraulic Motor</t>
-  </si>
-  <si>
     <t>Burnish Hydraulic Pump</t>
   </si>
   <si>
@@ -129,6 +123,18 @@
   </si>
   <si>
     <t>t2</t>
+  </si>
+  <si>
+    <t>Burnish 'Coolant Motor_DE</t>
+  </si>
+  <si>
+    <t>Burnish 'Coolant Motor_NDE</t>
+  </si>
+  <si>
+    <t>Burnish Hydraulic Motor_MDE</t>
+  </si>
+  <si>
+    <t>Burnish Hydraulic Motor_MNDE</t>
   </si>
 </sst>
 </file>
@@ -589,10 +595,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1">
         <f>F2+1.5*G2</f>
@@ -614,10 +620,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" ref="D3:D56" si="0">F3+1.5*G3</f>
@@ -639,10 +645,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
@@ -664,10 +670,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
@@ -689,10 +695,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
@@ -714,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
@@ -739,10 +745,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
@@ -764,10 +770,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
@@ -789,10 +795,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
@@ -814,10 +820,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
@@ -839,10 +845,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
@@ -864,10 +870,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
@@ -889,10 +895,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
@@ -914,10 +920,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
@@ -939,10 +945,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
@@ -964,10 +970,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
@@ -989,10 +995,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="0"/>
@@ -1014,10 +1020,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="0"/>
@@ -1039,10 +1045,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
@@ -1064,10 +1070,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="0"/>
@@ -1089,10 +1095,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="0"/>
@@ -1114,10 +1120,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
@@ -1139,10 +1145,10 @@
         <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="0"/>
@@ -1164,10 +1170,10 @@
         <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
@@ -1189,10 +1195,10 @@
         <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="0"/>
@@ -1214,10 +1220,10 @@
         <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="0"/>
@@ -1239,10 +1245,10 @@
         <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
@@ -1264,10 +1270,10 @@
         <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="0"/>
@@ -1289,10 +1295,10 @@
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
@@ -1314,10 +1320,10 @@
         <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
@@ -1339,10 +1345,10 @@
         <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D32" s="1">
         <f t="shared" si="0"/>
@@ -1364,10 +1370,10 @@
         <v>13</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D33" s="1">
         <f t="shared" si="0"/>
@@ -1389,10 +1395,10 @@
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" si="0"/>
@@ -1414,10 +1420,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D35" s="1">
         <f t="shared" si="0"/>
@@ -1439,10 +1445,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1">
         <f t="shared" si="0"/>
@@ -1464,10 +1470,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
@@ -1489,10 +1495,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="0"/>
@@ -1514,10 +1520,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" si="0"/>
@@ -1539,10 +1545,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="0"/>
@@ -1564,10 +1570,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
@@ -1589,10 +1595,10 @@
         <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="0"/>
@@ -1614,10 +1620,10 @@
         <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" si="0"/>
@@ -1639,10 +1645,10 @@
         <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" si="0"/>
@@ -1664,10 +1670,10 @@
         <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D45" s="1">
         <f t="shared" si="0"/>
@@ -1689,10 +1695,10 @@
         <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" si="0"/>
@@ -1714,10 +1720,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" si="0"/>
@@ -1739,10 +1745,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" si="0"/>
@@ -1764,10 +1770,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" si="0"/>
@@ -1789,10 +1795,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" si="0"/>
@@ -1814,10 +1820,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D51" s="1">
         <f t="shared" si="0"/>
@@ -1839,10 +1845,10 @@
         <v>17</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="0"/>
@@ -1864,10 +1870,10 @@
         <v>17</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="0"/>
@@ -1889,10 +1895,10 @@
         <v>17</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D54" s="1">
         <f t="shared" si="0"/>
@@ -1914,10 +1920,10 @@
         <v>17</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D55" s="1">
         <f t="shared" si="0"/>
@@ -1939,10 +1945,10 @@
         <v>17</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D56" s="1">
         <f t="shared" si="0"/>
